--- a/resource/data_uji.xlsx
+++ b/resource/data_uji.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f4ed61fe0626ee0/Documents/Skripsi/resource/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{E5FB141B-1DFD-4E19-8B67-446BC7D85C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6FE0C06-595F-4855-A653-451F5ACB6BBA}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{E5FB141B-1DFD-4E19-8B67-446BC7D85C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0B92E93-8014-4CF2-9598-D28B9E9FDBF3}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{EBA6B8CB-333D-49C0-AF5E-CC75C6136B31}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBA6B8CB-333D-49C0-AF5E-CC75C6136B31}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="183">
   <si>
     <t>Sensor</t>
   </si>
@@ -531,18 +531,9 @@
     <t>Google Maps</t>
   </si>
   <si>
-    <t>Long</t>
-  </si>
-  <si>
-    <t>Lat</t>
-  </si>
-  <si>
     <t>Selisih Jarak</t>
   </si>
   <si>
-    <t>25.18 Meter</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -550,6 +541,39 @@
   </si>
   <si>
     <t>TDS Air</t>
+  </si>
+  <si>
+    <t>Longitude, Latitude</t>
+  </si>
+  <si>
+    <t>-6.355106, 106.775095</t>
+  </si>
+  <si>
+    <t>-6.354897, 106.77518</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -6.312764, 106.793327</t>
+  </si>
+  <si>
+    <t>-6.312687,106.793267</t>
+  </si>
+  <si>
+    <t>-6.312764, 106.793328</t>
+  </si>
+  <si>
+    <t>-6.312687,106.793268</t>
+  </si>
+  <si>
+    <t>-6.312687,106.793269</t>
+  </si>
+  <si>
+    <t>-6.312687,106.793270</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -6.312765, 106.793329</t>
+  </si>
+  <si>
+    <t>-6.312765, 106.793330</t>
   </si>
 </sst>
 </file>
@@ -559,7 +583,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,6 +603,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -613,7 +643,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -673,12 +703,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -699,36 +749,11 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -744,11 +769,53 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3463,7 +3530,7 @@
   <cols>
     <col min="2" max="2" width="11.21875" customWidth="1"/>
     <col min="3" max="3" width="21.21875" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
     <col min="5" max="5" width="15.5546875" customWidth="1"/>
     <col min="7" max="7" width="9.21875" customWidth="1"/>
     <col min="8" max="8" width="18.109375" customWidth="1"/>
@@ -3529,53 +3596,53 @@
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="I2" s="17"/>
+      <c r="H2" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I2" s="29"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15" t="s">
+      <c r="M2" s="22"/>
+      <c r="N2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="15"/>
+      <c r="O2" s="22"/>
       <c r="P2" s="9"/>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="15"/>
+      <c r="R2" s="22"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="15" t="s">
+      <c r="T2" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="U2" s="15"/>
+      <c r="U2" s="22"/>
       <c r="V2" s="9"/>
-      <c r="W2" s="15" t="s">
+      <c r="W2" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="X2" s="15"/>
+      <c r="X2" s="22"/>
       <c r="Y2" s="9"/>
-      <c r="Z2" s="15" t="s">
+      <c r="Z2" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="AA2" s="15"/>
+      <c r="AA2" s="22"/>
       <c r="AB2" s="9"/>
-      <c r="AF2" s="23"/>
-      <c r="AG2" s="24" t="s">
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="26"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="24" t="s">
+      <c r="AH2" s="18"/>
+      <c r="AI2" s="19"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="AL2" s="25"/>
-      <c r="AM2" s="26"/>
+      <c r="AL2" s="18"/>
+      <c r="AM2" s="19"/>
       <c r="AN2" s="9"/>
     </row>
     <row r="3" spans="1:60" x14ac:dyDescent="0.3">
@@ -3647,7 +3714,7 @@
       <c r="AE3">
         <v>0</v>
       </c>
-      <c r="AF3" s="23"/>
+      <c r="AF3" s="14"/>
       <c r="AG3" s="6" t="s">
         <v>160</v>
       </c>
@@ -3657,7 +3724,7 @@
       <c r="AI3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AJ3" s="23"/>
+      <c r="AJ3" s="14"/>
       <c r="AK3" s="6" t="s">
         <v>160</v>
       </c>
@@ -3738,7 +3805,7 @@
       <c r="AE4">
         <v>0</v>
       </c>
-      <c r="AF4" s="23"/>
+      <c r="AF4" s="14"/>
       <c r="AG4" s="5">
         <v>0</v>
       </c>
@@ -3748,7 +3815,7 @@
       <c r="AI4" s="5">
         <v>0</v>
       </c>
-      <c r="AJ4" s="23"/>
+      <c r="AJ4" s="14"/>
       <c r="AK4" s="5">
         <v>529.4</v>
       </c>
@@ -3847,7 +3914,7 @@
       <c r="AE5">
         <v>0</v>
       </c>
-      <c r="AF5" s="23"/>
+      <c r="AF5" s="14"/>
       <c r="AG5" s="5">
         <v>0</v>
       </c>
@@ -3857,7 +3924,7 @@
       <c r="AI5" s="5">
         <v>0</v>
       </c>
-      <c r="AJ5" s="23"/>
+      <c r="AJ5" s="14"/>
       <c r="AK5" s="5">
         <v>534</v>
       </c>
@@ -3956,7 +4023,7 @@
       <c r="AE6">
         <v>0</v>
       </c>
-      <c r="AF6" s="23"/>
+      <c r="AF6" s="14"/>
       <c r="AG6" s="5">
         <v>0</v>
       </c>
@@ -3966,7 +4033,7 @@
       <c r="AI6" s="5">
         <v>0</v>
       </c>
-      <c r="AJ6" s="23"/>
+      <c r="AJ6" s="14"/>
       <c r="AK6" s="5">
         <v>530.5</v>
       </c>
@@ -4065,7 +4132,7 @@
       <c r="AE7">
         <v>0</v>
       </c>
-      <c r="AF7" s="23"/>
+      <c r="AF7" s="14"/>
       <c r="AG7" s="5">
         <v>0</v>
       </c>
@@ -4075,7 +4142,7 @@
       <c r="AI7" s="5">
         <v>0</v>
       </c>
-      <c r="AJ7" s="23"/>
+      <c r="AJ7" s="14"/>
       <c r="AK7" s="5">
         <v>547</v>
       </c>
@@ -4176,7 +4243,7 @@
         <f>AVERAGE(AE3:AE7)</f>
         <v>0</v>
       </c>
-      <c r="AF8" s="23"/>
+      <c r="AF8" s="14"/>
       <c r="AG8" s="5">
         <v>0</v>
       </c>
@@ -4186,7 +4253,7 @@
       <c r="AI8" s="5">
         <v>0</v>
       </c>
-      <c r="AJ8" s="23"/>
+      <c r="AJ8" s="14"/>
       <c r="AK8" s="5">
         <v>551.5</v>
       </c>
@@ -4321,7 +4388,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ9" s="23"/>
+      <c r="AJ9" s="14"/>
       <c r="AK9" s="5">
         <f t="shared" si="1"/>
         <v>538.48</v>
@@ -4375,20 +4442,20 @@
       <c r="G10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="24">
         <f>ABS((H9-I9)/I9)</f>
         <v>1.8803418803418827E-2</v>
       </c>
-      <c r="I10" s="19"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="9"/>
       <c r="K10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="23">
         <f>ABS((24.238-24)/24)</f>
         <v>9.9166666666666483E-3</v>
       </c>
-      <c r="M10" s="14"/>
+      <c r="M10" s="23"/>
       <c r="N10" s="9"/>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
@@ -4413,18 +4480,18 @@
       <c r="AF10" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="AG10" s="27">
+      <c r="AG10" s="20">
         <v>0</v>
       </c>
-      <c r="AH10" s="27"/>
-      <c r="AI10" s="27"/>
-      <c r="AJ10" s="23"/>
-      <c r="AK10" s="28">
+      <c r="AH10" s="20"/>
+      <c r="AI10" s="20"/>
+      <c r="AJ10" s="14"/>
+      <c r="AK10" s="21">
         <f>ABS((AK9-AM9)/AM9)</f>
         <v>1.7055988134964018E-3</v>
       </c>
-      <c r="AL10" s="28"/>
-      <c r="AM10" s="28"/>
+      <c r="AL10" s="21"/>
+      <c r="AM10" s="21"/>
       <c r="AN10" s="9"/>
       <c r="AY10" t="s">
         <v>114</v>
@@ -4448,7 +4515,7 @@
     <row r="11" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C11" s="12">
         <f>1-C10</f>
@@ -4464,22 +4531,22 @@
       </c>
       <c r="F11" s="10"/>
       <c r="G11" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="H11" s="20">
+        <v>170</v>
+      </c>
+      <c r="H11" s="26">
         <f>1-H10</f>
         <v>0.98119658119658115</v>
       </c>
-      <c r="I11" s="21"/>
+      <c r="I11" s="27"/>
       <c r="J11" s="9"/>
       <c r="K11" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="L11" s="22">
+        <v>170</v>
+      </c>
+      <c r="L11" s="30">
         <f>1-L10</f>
         <v>0.99008333333333332</v>
       </c>
-      <c r="M11" s="22"/>
+      <c r="M11" s="30"/>
       <c r="AD11">
         <v>1.282</v>
       </c>
@@ -4487,21 +4554,21 @@
         <v>8.6199999999999992</v>
       </c>
       <c r="AF11" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="AG11" s="27">
+        <v>170</v>
+      </c>
+      <c r="AG11" s="20">
         <f>1-AG10</f>
         <v>1</v>
       </c>
-      <c r="AH11" s="27"/>
-      <c r="AI11" s="27"/>
-      <c r="AJ11" s="23"/>
-      <c r="AK11" s="28">
+      <c r="AH11" s="20"/>
+      <c r="AI11" s="20"/>
+      <c r="AJ11" s="14"/>
+      <c r="AK11" s="21">
         <f>1-AK10</f>
         <v>0.99829440118650359</v>
       </c>
-      <c r="AL11" s="28"/>
-      <c r="AM11" s="28"/>
+      <c r="AL11" s="21"/>
+      <c r="AM11" s="21"/>
       <c r="AN11" s="9"/>
       <c r="AY11" t="s">
         <v>119</v>
@@ -5333,58 +5400,61 @@
     </row>
     <row r="41" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="D41" s="31"/>
+      <c r="E41" s="41" t="s">
+        <v>168</v>
+      </c>
       <c r="AZ41" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="30" t="s">
+      <c r="B42" s="33"/>
+      <c r="C42" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="E42" s="9"/>
+      <c r="E42" s="41"/>
       <c r="AZ42" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
-      <c r="B43" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="C43" s="31">
-        <v>-6.3551060000000001</v>
-      </c>
-      <c r="D43" s="31">
-        <v>-6.3548970000000002</v>
-      </c>
-      <c r="E43" s="9"/>
+      <c r="C43" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="E43" s="35">
+        <v>25.18</v>
+      </c>
+      <c r="F43" s="40"/>
       <c r="AZ43" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
-      <c r="B44" s="30" t="s">
+      <c r="C44" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="E44" s="3">
+        <v>10.83</v>
+      </c>
+      <c r="J44" t="s">
         <v>169</v>
-      </c>
-      <c r="C44" s="31">
-        <v>106.77509499999999</v>
-      </c>
-      <c r="D44" s="31">
-        <v>106.77518000000001</v>
-      </c>
-      <c r="E44" s="9"/>
-      <c r="J44" t="s">
-        <v>172</v>
       </c>
       <c r="AZ44" t="s">
         <v>112</v>
@@ -5392,28 +5462,52 @@
     </row>
     <row r="45" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
-      <c r="B45" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="C45" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="D45" s="32"/>
-      <c r="E45" s="9"/>
+      <c r="C45" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10.9</v>
+      </c>
     </row>
     <row r="46" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
+      <c r="C46" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10.99</v>
+      </c>
     </row>
     <row r="47" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="C47" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E47" s="3">
+        <v>11.05</v>
+      </c>
       <c r="AZ47" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="C48" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="39"/>
+      <c r="E48" s="3">
+        <f>AVERAGE(E43:E47)</f>
+        <v>13.790000000000001</v>
+      </c>
       <c r="AZ48" t="s">
         <v>76</v>
       </c>
@@ -5454,10 +5548,17 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="21">
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="AG11:AI11"/>
     <mergeCell ref="AK11:AM11"/>
-    <mergeCell ref="C45:D45"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="Q2:R2"/>
@@ -5469,11 +5570,8 @@
     <mergeCell ref="AK10:AM10"/>
     <mergeCell ref="AG10:AI10"/>
     <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="AG2:AI2"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/resource/data_uji.xlsx
+++ b/resource/data_uji.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f4ed61fe0626ee0/Documents/Skripsi/resource/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Afit\OneDrive\Documents\Skripsi\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{E5FB141B-1DFD-4E19-8B67-446BC7D85C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0B92E93-8014-4CF2-9598-D28B9E9FDBF3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6296C87-0563-427B-B1A9-4A72486B7C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBA6B8CB-333D-49C0-AF5E-CC75C6136B31}"/>
   </bookViews>
@@ -728,7 +728,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -754,6 +754,28 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -768,9 +790,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -795,27 +814,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2039,6 +2037,355 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$52:$H$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>3.06</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6219999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2570000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$52:$I$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.85</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A6BE-4A42-8852-E79D40B31AFC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1167725999"/>
+        <c:axId val="1167726479"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1167725999"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1167726479"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1167726479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1167725999"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2119,6 +2466,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2636,6 +3023,522 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3220,6 +4123,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1097935</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>119627</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>417871</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>158956</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6822FCE6-81C2-F8C1-CC6F-A9E1BABFE555}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3596,53 +4535,53 @@
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="I2" s="29"/>
+      <c r="I2" s="38"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
-      <c r="L2" s="22" t="s">
+      <c r="L2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22" t="s">
+      <c r="M2" s="23"/>
+      <c r="N2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="22"/>
+      <c r="O2" s="23"/>
       <c r="P2" s="9"/>
-      <c r="Q2" s="22" t="s">
+      <c r="Q2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="22"/>
+      <c r="R2" s="23"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="22" t="s">
+      <c r="T2" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="U2" s="22"/>
+      <c r="U2" s="23"/>
       <c r="V2" s="9"/>
-      <c r="W2" s="22" t="s">
+      <c r="W2" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="X2" s="22"/>
+      <c r="X2" s="23"/>
       <c r="Y2" s="9"/>
-      <c r="Z2" s="22" t="s">
+      <c r="Z2" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="AA2" s="22"/>
+      <c r="AA2" s="23"/>
       <c r="AB2" s="9"/>
       <c r="AF2" s="14"/>
-      <c r="AG2" s="17" t="s">
+      <c r="AG2" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="AH2" s="18"/>
-      <c r="AI2" s="19"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="29"/>
       <c r="AJ2" s="14"/>
-      <c r="AK2" s="17" t="s">
+      <c r="AK2" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="19"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="29"/>
       <c r="AN2" s="9"/>
     </row>
     <row r="3" spans="1:60" x14ac:dyDescent="0.3">
@@ -4442,20 +5381,20 @@
       <c r="G10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="33">
         <f>ABS((H9-I9)/I9)</f>
         <v>1.8803418803418827E-2</v>
       </c>
-      <c r="I10" s="25"/>
+      <c r="I10" s="34"/>
       <c r="J10" s="9"/>
       <c r="K10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="23">
+      <c r="L10" s="32">
         <f>ABS((24.238-24)/24)</f>
         <v>9.9166666666666483E-3</v>
       </c>
-      <c r="M10" s="23"/>
+      <c r="M10" s="32"/>
       <c r="N10" s="9"/>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
@@ -4480,18 +5419,18 @@
       <c r="AF10" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="AG10" s="20">
+      <c r="AG10" s="30">
         <v>0</v>
       </c>
-      <c r="AH10" s="20"/>
-      <c r="AI10" s="20"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="30"/>
       <c r="AJ10" s="14"/>
-      <c r="AK10" s="21">
+      <c r="AK10" s="31">
         <f>ABS((AK9-AM9)/AM9)</f>
         <v>1.7055988134964018E-3</v>
       </c>
-      <c r="AL10" s="21"/>
-      <c r="AM10" s="21"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="31"/>
       <c r="AN10" s="9"/>
       <c r="AY10" t="s">
         <v>114</v>
@@ -4533,20 +5472,20 @@
       <c r="G11" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="35">
         <f>1-H10</f>
         <v>0.98119658119658115</v>
       </c>
-      <c r="I11" s="27"/>
+      <c r="I11" s="36"/>
       <c r="J11" s="9"/>
       <c r="K11" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="39">
         <f>1-L10</f>
         <v>0.99008333333333332</v>
       </c>
-      <c r="M11" s="30"/>
+      <c r="M11" s="39"/>
       <c r="AD11">
         <v>1.282</v>
       </c>
@@ -4556,19 +5495,19 @@
       <c r="AF11" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="AG11" s="20">
+      <c r="AG11" s="30">
         <f>1-AG10</f>
         <v>1</v>
       </c>
-      <c r="AH11" s="20"/>
-      <c r="AI11" s="20"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="30"/>
       <c r="AJ11" s="14"/>
-      <c r="AK11" s="21">
+      <c r="AK11" s="31">
         <f>1-AK10</f>
         <v>0.99829440118650359</v>
       </c>
-      <c r="AL11" s="21"/>
-      <c r="AM11" s="21"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="31"/>
       <c r="AN11" s="9"/>
       <c r="AY11" t="s">
         <v>119</v>
@@ -5400,12 +6339,12 @@
     </row>
     <row r="41" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="31" t="s">
+      <c r="B41" s="25"/>
+      <c r="C41" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="D41" s="31"/>
-      <c r="E41" s="41" t="s">
+      <c r="D41" s="24"/>
+      <c r="E41" s="22" t="s">
         <v>168</v>
       </c>
       <c r="AZ41" t="s">
@@ -5414,30 +6353,30 @@
     </row>
     <row r="42" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
-      <c r="B42" s="33"/>
+      <c r="B42" s="26"/>
       <c r="C42" s="15" t="s">
         <v>166</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="E42" s="41"/>
+      <c r="E42" s="22"/>
       <c r="AZ42" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
-      <c r="C43" s="34" t="s">
+      <c r="C43" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="D43" s="34" t="s">
+      <c r="D43" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="E43" s="35">
+      <c r="E43" s="16">
         <v>25.18</v>
       </c>
-      <c r="F43" s="40"/>
+      <c r="F43" s="20"/>
       <c r="AZ43" t="s">
         <v>111</v>
       </c>
@@ -5462,7 +6401,7 @@
     </row>
     <row r="45" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
-      <c r="C45" s="36" t="s">
+      <c r="C45" s="17" t="s">
         <v>177</v>
       </c>
       <c r="D45" s="16" t="s">
@@ -5475,7 +6414,7 @@
     <row r="46" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
-      <c r="C46" s="37" t="s">
+      <c r="C46" s="18" t="s">
         <v>181</v>
       </c>
       <c r="D46" s="16" t="s">
@@ -5486,7 +6425,7 @@
       </c>
     </row>
     <row r="47" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="C47" s="38" t="s">
+      <c r="C47" s="19" t="s">
         <v>182</v>
       </c>
       <c r="D47" s="16" t="s">
@@ -5500,10 +6439,10 @@
       </c>
     </row>
     <row r="48" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="C48" s="39" t="s">
+      <c r="C48" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D48" s="39"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="3">
         <f>AVERAGE(E43:E47)</f>
         <v>13.790000000000001</v>
@@ -5512,48 +6451,61 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" spans="52:52" x14ac:dyDescent="0.3">
+    <row r="49" spans="8:52" x14ac:dyDescent="0.3">
       <c r="AZ49" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="50" spans="52:52" x14ac:dyDescent="0.3">
+    <row r="50" spans="8:52" x14ac:dyDescent="0.3">
       <c r="AZ50" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="51" spans="52:52" x14ac:dyDescent="0.3">
+    <row r="51" spans="8:52" x14ac:dyDescent="0.3">
       <c r="AZ51" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="52:52" x14ac:dyDescent="0.3">
+    <row r="52" spans="8:52" x14ac:dyDescent="0.3">
+      <c r="H52">
+        <v>3.06</v>
+      </c>
+      <c r="I52">
+        <v>4.01</v>
+      </c>
       <c r="AZ52" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="53" spans="52:52" x14ac:dyDescent="0.3">
+    <row r="53" spans="8:52" x14ac:dyDescent="0.3">
+      <c r="H53">
+        <v>2.6219999999999999</v>
+      </c>
+      <c r="I53">
+        <v>6.85</v>
+      </c>
       <c r="AZ53" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="52:52" x14ac:dyDescent="0.3">
+    <row r="54" spans="8:52" x14ac:dyDescent="0.3">
+      <c r="H54">
+        <v>2.2570000000000001</v>
+      </c>
+      <c r="I54">
+        <v>9.14</v>
+      </c>
       <c r="AZ54" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="52:52" x14ac:dyDescent="0.3">
+    <row r="56" spans="8:52" x14ac:dyDescent="0.3">
       <c r="AZ56">
         <v>1.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="C41:D41"/>
     <mergeCell ref="B41:B42"/>
     <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="AG2:AI2"/>
@@ -5570,6 +6522,11 @@
     <mergeCell ref="AK10:AM10"/>
     <mergeCell ref="AG10:AI10"/>
     <mergeCell ref="W2:X2"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="C41:D41"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
